--- a/artfynd/A 15355-2026 artfynd.xlsx
+++ b/artfynd/A 15355-2026 artfynd.xlsx
@@ -1216,7 +1216,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 15355-2026 artfynd.xlsx
+++ b/artfynd/A 15355-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132799793</v>
       </c>
       <c r="B2" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>132799885</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>132800038</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
         <v>132799972</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>132800098</v>
       </c>
       <c r="B6" t="n">
-        <v>80461</v>
+        <v>80462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 15355-2026 artfynd.xlsx
+++ b/artfynd/A 15355-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132799793</v>
+        <v>132799885</v>
       </c>
       <c r="B2" t="n">
-        <v>80438</v>
+        <v>57955</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Täxtberget, Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781876</v>
+        <v>781875</v>
       </c>
       <c r="R2" t="n">
-        <v>7296159</v>
+        <v>7296147</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132799885</v>
+        <v>132799793</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>80438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Täxtberget, Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781875</v>
+        <v>781876</v>
       </c>
       <c r="R3" t="n">
-        <v>7296147</v>
+        <v>7296159</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 15355-2026 artfynd.xlsx
+++ b/artfynd/A 15355-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132799885</v>
+        <v>132799793</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>80438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Täxtberget, Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781875</v>
+        <v>781876</v>
       </c>
       <c r="R2" t="n">
-        <v>7296147</v>
+        <v>7296159</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132799793</v>
+        <v>132799885</v>
       </c>
       <c r="B3" t="n">
-        <v>80438</v>
+        <v>57955</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Täxtberget, Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781876</v>
+        <v>781875</v>
       </c>
       <c r="R3" t="n">
-        <v>7296159</v>
+        <v>7296147</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 15355-2026 artfynd.xlsx
+++ b/artfynd/A 15355-2026 artfynd.xlsx
@@ -1002,7 +1002,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 15355-2026 artfynd.xlsx
+++ b/artfynd/A 15355-2026 artfynd.xlsx
@@ -1124,7 +1124,7 @@
         <v>132800098</v>
       </c>
       <c r="B6" t="n">
-        <v>80467</v>
+        <v>80468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15355-2026 artfynd.xlsx
+++ b/artfynd/A 15355-2026 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132799793</v>
+        <v>132799822</v>
       </c>
       <c r="B2" t="n">
-        <v>80438</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Täxtberget, Täxtberget, Nb</t>
+          <t>Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>781876</v>
+        <v>781862</v>
       </c>
       <c r="R2" t="n">
-        <v>7296159</v>
+        <v>7296134</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre bestånd gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132799885</v>
+        <v>132799793</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>80488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Täxtberget, Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>781875</v>
+        <v>781876</v>
       </c>
       <c r="R3" t="n">
-        <v>7296147</v>
+        <v>7296159</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -860,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,32 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132799822</v>
+        <v>132800098</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>80493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,12 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre bestånd gran</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,34 +994,34 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132799972</v>
+        <v>132799885</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1038,19 +1030,27 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Täxtberget, Nb</t>
+          <t>Täxtberget, Täxtberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>781862</v>
+        <v>781875</v>
       </c>
       <c r="R5" t="n">
-        <v>7296134</v>
+        <v>7296147</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,12 +1089,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Riklig förekomst av ringhack på flera granar.</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,44 +1104,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132800098</v>
+        <v>132799972</v>
       </c>
       <c r="B6" t="n">
-        <v>80468</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1201,7 +1196,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Riklig förekomst av ringhack på flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 15355-2026 artfynd.xlsx
+++ b/artfynd/A 15355-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132799822</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132799793</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132800098</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132799885</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,8 +1250,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132799972</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>